--- a/survey_templates/035_mix2x_user_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/035_mix2x_user_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Almost always'}</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
